--- a/preorder_forms/047_school_play_costumes_pre_order_form--preorder_forms.xlsx
+++ b/preorder_forms/047_school_play_costumes_pre_order_form--preorder_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1126,8 +1126,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'costume_1',_'value':_'costume_1'}</t>
+          <t>costume_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Costume 1', 'value': 'costume_1'}</t>
+          <t>Costume 1</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'costume_2',_'value':_'costume_2'}</t>
+          <t>costume_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Costume 2', 'value': 'costume_2'}</t>
+          <t>Costume 2</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'delivery_1',_'value':_'delivery_1'}</t>
+          <t>delivery_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Delivery 1', 'value': 'delivery_1'}</t>
+          <t>Delivery 1</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'delivery_2',_'value':_'delivery_2'}</t>
+          <t>delivery_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Delivery 2', 'value': 'delivery_2'}</t>
+          <t>Delivery 2</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'delivery_3',_'value':_'delivery_3'}</t>
+          <t>delivery_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Delivery 3', 'value': 'delivery_3'}</t>
+          <t>Delivery 3</t>
         </is>
       </c>
     </row>
